--- a/tmk/presupuesto_TMK.xlsx
+++ b/tmk/presupuesto_TMK.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,8 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$I$21</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -71,34 +74,34 @@
     <t>Venta directa - salarial</t>
   </si>
   <si>
+    <t>Líder</t>
+  </si>
+  <si>
+    <t>Maria Deisy Gil Gomez</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Referido - bono</t>
+  </si>
+  <si>
+    <t>Pyme Móvil - salarial</t>
+  </si>
+  <si>
+    <t>CLOUND - salarial</t>
+  </si>
+  <si>
     <t>Auxiliar</t>
   </si>
   <si>
     <t>Natalia  Giraldo Galeano</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
     <t>Raiza Lorena Urzola Lora</t>
   </si>
   <si>
     <t>Yessica Yulieth Moreno</t>
-  </si>
-  <si>
-    <t>Referido - bono</t>
-  </si>
-  <si>
-    <t>Líder</t>
-  </si>
-  <si>
-    <t>Maria Deisy Gil Gomez</t>
-  </si>
-  <si>
-    <t>Pyme Móvil - salarial</t>
-  </si>
-  <si>
-    <t>CLOUND - salarial</t>
   </si>
   <si>
     <t>Febrero</t>
@@ -112,7 +115,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -484,7 +487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -493,7 +496,7 @@
     <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -533,10 +536,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -551,7 +554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -559,13 +562,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>150</v>
@@ -580,7 +583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -588,13 +591,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -609,7 +612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -617,13 +620,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -638,7 +641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -649,10 +652,10 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>20</v>
@@ -667,7 +670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -675,13 +678,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>40</v>
@@ -696,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>2026</v>
       </c>
@@ -707,10 +710,10 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F8">
         <v>20</v>
@@ -725,7 +728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>2026</v>
       </c>
@@ -733,13 +736,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -754,7 +757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -765,10 +768,10 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>20</v>
@@ -783,7 +786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>2026</v>
       </c>
@@ -791,13 +794,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>40</v>
@@ -812,7 +815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -823,10 +826,10 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>75</v>
@@ -842,7 +845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -850,13 +853,13 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F13">
         <v>150</v>
@@ -872,7 +875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -880,13 +883,13 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <v>60</v>
@@ -902,7 +905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>2026</v>
       </c>
@@ -910,13 +913,13 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4">
         <v>100000</v>
@@ -932,7 +935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>2026</v>
       </c>
@@ -943,10 +946,10 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F16">
         <v>25</v>
@@ -962,7 +965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>2026</v>
       </c>
@@ -970,13 +973,13 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -992,7 +995,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -1003,10 +1006,10 @@
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18">
         <v>25</v>
@@ -1022,7 +1025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -1030,13 +1033,13 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19">
         <v>50</v>
@@ -1052,7 +1055,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>2026</v>
       </c>
@@ -1063,10 +1066,10 @@
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F20">
         <v>25</v>
@@ -1082,7 +1085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>2026</v>
       </c>
@@ -1090,13 +1093,13 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>50</v>
